--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104521_W7.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104521_W7.xlsx
@@ -565,58 +565,58 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.6666</v>
+        <v>7.3152</v>
       </c>
       <c r="E2" t="n">
-        <v>6.6991</v>
+        <v>7.198</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0325</v>
+        <v>0.1172</v>
       </c>
       <c r="G2" t="n">
-        <v>7.9259</v>
+        <v>7.9098</v>
       </c>
       <c r="H2" t="n">
-        <v>3.8744</v>
+        <v>3.869</v>
       </c>
       <c r="I2" t="n">
-        <v>4.0515</v>
+        <v>4.0409</v>
       </c>
       <c r="J2" t="n">
-        <v>8.649800000000001</v>
+        <v>8.6106</v>
       </c>
       <c r="K2" t="n">
-        <v>4.3638</v>
+        <v>4.3437</v>
       </c>
       <c r="L2" t="n">
-        <v>4.286</v>
+        <v>4.2669</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.7239</v>
+        <v>-0.7007</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.4894</v>
+        <v>-0.4747</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.2345</v>
+        <v>-0.226</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.2594</v>
+        <v>-0.5947</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8166</v>
+        <v>-0.2744</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4428</v>
+        <v>-0.3202</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.7614</v>
+        <v>4.7018</v>
       </c>
       <c r="E3" t="n">
-        <v>5.6041</v>
+        <v>5.5893</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8427</v>
+        <v>-0.8875999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>6.3575</v>
+        <v>6.3567</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7199</v>
+        <v>0.7262999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>5.6375</v>
+        <v>5.6304</v>
       </c>
       <c r="J3" t="n">
-        <v>5.8824</v>
+        <v>5.8682</v>
       </c>
       <c r="K3" t="n">
-        <v>0.658</v>
+        <v>0.655</v>
       </c>
       <c r="L3" t="n">
-        <v>5.2243</v>
+        <v>5.2132</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4751</v>
+        <v>0.4886</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0619</v>
+        <v>0.0713</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4132</v>
+        <v>0.4173</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1839</v>
+        <v>-0.2483</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2782</v>
+        <v>-0.2788</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0944</v>
+        <v>0.0305</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.979</v>
+        <v>3.2691</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0168</v>
+        <v>0.799</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9622</v>
+        <v>2.4701</v>
       </c>
       <c r="G4" t="n">
-        <v>3.5815</v>
+        <v>3.5652</v>
       </c>
       <c r="H4" t="n">
-        <v>4.1546</v>
+        <v>4.134</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5731000000000001</v>
+        <v>-0.5688</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9327</v>
+        <v>2.8867</v>
       </c>
       <c r="K4" t="n">
-        <v>3.6845</v>
+        <v>3.6467</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.7517</v>
+        <v>-0.7601</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6488</v>
+        <v>0.6785</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4701</v>
+        <v>0.4873</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1787</v>
+        <v>0.1912</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0977</v>
+        <v>-0.8</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3962</v>
+        <v>-0.5625</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2985</v>
+        <v>-0.2375</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.1314</v>
+        <v>2.4831</v>
       </c>
       <c r="E5" t="n">
-        <v>2.7191</v>
+        <v>1.822</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4123</v>
+        <v>0.6611</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5733</v>
+        <v>1.5735</v>
       </c>
       <c r="H5" t="n">
-        <v>1.368</v>
+        <v>1.3617</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2053</v>
+        <v>0.2118</v>
       </c>
       <c r="J5" t="n">
-        <v>1.7509</v>
+        <v>1.7295</v>
       </c>
       <c r="K5" t="n">
-        <v>1.527</v>
+        <v>1.5061</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2239</v>
+        <v>0.2234</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1776</v>
+        <v>-0.156</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.159</v>
+        <v>-0.1444</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0186</v>
+        <v>-0.0116</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5846</v>
+        <v>-0.0708</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8075</v>
+        <v>-0.0653</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2229</v>
+        <v>-0.0055</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="6">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5902</v>
+        <v>1.9421</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2411</v>
+        <v>-0.1985</v>
       </c>
       <c r="F6" t="n">
-        <v>1.8313</v>
+        <v>2.1406</v>
       </c>
       <c r="G6" t="n">
-        <v>2.3067</v>
+        <v>2.308</v>
       </c>
       <c r="H6" t="n">
-        <v>1.4617</v>
+        <v>1.4619</v>
       </c>
       <c r="I6" t="n">
-        <v>0.845</v>
+        <v>0.8462</v>
       </c>
       <c r="J6" t="n">
-        <v>2.3538</v>
+        <v>2.3337</v>
       </c>
       <c r="K6" t="n">
-        <v>1.2743</v>
+        <v>1.2615</v>
       </c>
       <c r="L6" t="n">
-        <v>1.0795</v>
+        <v>1.0722</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0471</v>
+        <v>-0.0257</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1874</v>
+        <v>0.2003</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2345</v>
+        <v>-0.226</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R6" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.1701</v>
+        <v>-0.8212</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3266</v>
+        <v>-0.2559</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8435</v>
+        <v>-0.5653</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2887</v>
+        <v>1.6515</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3619</v>
+        <v>0.7745</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9267</v>
+        <v>0.877</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4926</v>
+        <v>0.4902</v>
       </c>
       <c r="H7" t="n">
-        <v>1.2843</v>
+        <v>1.2811</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7917</v>
+        <v>-0.791</v>
       </c>
       <c r="J7" t="n">
-        <v>0.988</v>
+        <v>0.9768</v>
       </c>
       <c r="K7" t="n">
-        <v>1.6624</v>
+        <v>1.6547</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6744</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4954</v>
+        <v>-0.4866</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3781</v>
+        <v>-0.3736</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1172</v>
+        <v>-0.113</v>
       </c>
       <c r="P7" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7917999999999999</v>
+        <v>-0.4321</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6261</v>
+        <v>-0.2023</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1657</v>
+        <v>-0.2298</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3242</v>
+        <v>-0.6143</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3501</v>
+        <v>-0.7321</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0259</v>
+        <v>0.1178</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.0597</v>
+        <v>-1.0809</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.593</v>
+        <v>-0.5944</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4666</v>
+        <v>-0.4865</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3248</v>
+        <v>-0.367</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.3086</v>
+        <v>-0.321</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0162</v>
+        <v>-0.046</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.7348</v>
+        <v>-0.7139</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2844</v>
+        <v>-0.2734</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4504</v>
+        <v>-0.4405</v>
       </c>
       <c r="P8" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.8939</v>
+        <v>-1.1754</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0253</v>
+        <v>-0.3651</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8686</v>
+        <v>-0.8104</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. VESELY</t>
+          <t>T. SATORANSKY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9643</v>
+        <v>-1.7179</v>
       </c>
       <c r="E9" t="n">
-        <v>0.218</v>
+        <v>-1.1798</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.1823</v>
+        <v>-0.5381</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.9316</v>
+        <v>0.2809</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8627</v>
+        <v>0.4389</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.0689</v>
+        <v>-0.1579</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.914</v>
+        <v>0.5788</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6101</v>
+        <v>0.2963</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.3039</v>
+        <v>0.2826</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.0176</v>
+        <v>-0.2979</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2526</v>
+        <v>0.1426</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7649</v>
+        <v>-0.4405</v>
       </c>
       <c r="P9" t="n">
-        <v>1.8147</v>
+        <v>0.6829</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.594</v>
+        <v>-1.0475</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0393</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6333</v>
+        <v>-0.427</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2534</v>
+        <v>-1.6342</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.3461</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T. SATORANSKY</t>
+          <t>J. VESELY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4047</v>
+        <v>-1.768</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5799</v>
+        <v>0.2594</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8248</v>
+        <v>-2.0274</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2711</v>
+        <v>-1.9421</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4284</v>
+        <v>-0.8726</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1573</v>
+        <v>-1.0696</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5977</v>
+        <v>-0.9412</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3046</v>
+        <v>-0.628</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2931</v>
+        <v>-0.3132</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3266</v>
+        <v>-1.0009</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1238</v>
+        <v>-0.2446</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4504</v>
+        <v>-0.7563</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6805</v>
+        <v>1.8211</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.7173</v>
+        <v>-0.3997</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0434</v>
+        <v>0.1111</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6739000000000001</v>
+        <v>-0.5108</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.639</v>
+        <v>-1.2472</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.639</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. PARRA</t>
+          <t>N. LAPROVITTOLA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.7806</v>
+        <v>-4.3533</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.915</v>
+        <v>-3.2717</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8656</v>
+        <v>-1.0816</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.8423</v>
+        <v>-4.2996</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.6249</v>
+        <v>-1.7894</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.2174</v>
+        <v>-2.5102</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.532</v>
+        <v>-3.3828</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6478</v>
+        <v>-1.2001</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.8842</v>
+        <v>-2.1827</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.3103</v>
+        <v>-0.9167999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.9771</v>
+        <v>-0.5893</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3331</v>
+        <v>-0.3275</v>
       </c>
       <c r="P11" t="n">
-        <v>1.361</v>
+        <v>0.9105</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.361</v>
+        <v>0.9105</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7933</v>
+        <v>0.1253</v>
       </c>
       <c r="T11" t="n">
-        <v>0.617</v>
+        <v>0.1111</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1763</v>
+        <v>0.0141</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>N. LAPROVITTOLA</t>
+          <t>J. PARRA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.4273</v>
+        <v>-4.6974</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.3249</v>
+        <v>-3.4502</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.1024</v>
+        <v>-1.2472</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.2964</v>
+        <v>-4.84</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.7907</v>
+        <v>-1.6147</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.5056</v>
+        <v>-3.2254</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.3642</v>
+        <v>-3.5497</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.1917</v>
+        <v>-0.6516999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.1725</v>
+        <v>-2.8979</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.9321</v>
+        <v>-1.2904</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.599</v>
+        <v>-0.9629</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.3331</v>
+        <v>-0.3275</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0544</v>
+        <v>-0.1337</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0393</v>
+        <v>0.0994</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0151</v>
+        <v>-0.2331</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.516200000000002</v>
+        <v>8.211899999999998</v>
       </c>
       <c r="E13" t="n">
-        <v>7.208000000000002</v>
+        <v>7.609899999999998</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3081000000000003</v>
+        <v>0.6018999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>10.3786</v>
+        <v>10.3217</v>
       </c>
       <c r="H13" t="n">
-        <v>8.420000000000002</v>
+        <v>8.401800000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>1.9587</v>
+        <v>1.919899999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>15.0203</v>
+        <v>14.7436</v>
       </c>
       <c r="K13" t="n">
-        <v>10.7164</v>
+        <v>10.5632</v>
       </c>
       <c r="L13" t="n">
-        <v>4.303900000000002</v>
+        <v>4.1805</v>
       </c>
       <c r="M13" t="n">
-        <v>-4.641500000000001</v>
+        <v>-4.421799999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.2964</v>
+        <v>-2.1614</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.3448</v>
+        <v>-2.2604</v>
       </c>
       <c r="P13" t="n">
-        <v>12.4758</v>
+        <v>12.5198</v>
       </c>
       <c r="Q13" t="n">
-        <v>-5.6709</v>
+        <v>-5.690900000000001</v>
       </c>
       <c r="R13" t="n">
-        <v>18.1467</v>
+        <v>18.2107</v>
       </c>
       <c r="S13" t="n">
-        <v>-6.275799999999999</v>
+        <v>-5.598100000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.009300000000001</v>
+        <v>-2.3032</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.2664</v>
+        <v>-3.295</v>
       </c>
       <c r="V13" t="n">
-        <v>-9.062900000000001</v>
+        <v>-9.0314</v>
       </c>
       <c r="W13" t="n">
-        <v>0.8678</v>
+        <v>0.8602999999999998</v>
       </c>
       <c r="X13" t="n">
-        <v>-9.9307</v>
+        <v>-9.891599999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.3717</v>
+        <v>2.0775</v>
       </c>
       <c r="E14" t="n">
-        <v>4.3886</v>
+        <v>4.0017</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.0169</v>
+        <v>-1.9243</v>
       </c>
       <c r="G14" t="n">
-        <v>1.3628</v>
+        <v>1.3639</v>
       </c>
       <c r="H14" t="n">
-        <v>0.723</v>
+        <v>0.7156</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6398</v>
+        <v>0.6484</v>
       </c>
       <c r="J14" t="n">
-        <v>3.0062</v>
+        <v>2.9818</v>
       </c>
       <c r="K14" t="n">
-        <v>1.7001</v>
+        <v>1.6785</v>
       </c>
       <c r="L14" t="n">
-        <v>1.3061</v>
+        <v>1.3033</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.6434</v>
+        <v>-1.6179</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.9771</v>
+        <v>-0.9629</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.6663</v>
+        <v>-0.6549</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R14" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S14" t="n">
-        <v>1.9804</v>
+        <v>1.6955</v>
       </c>
       <c r="T14" t="n">
-        <v>1.488</v>
+        <v>1.1401</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4924</v>
+        <v>0.5554</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.06419999999999999</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>1.0285</v>
+        <v>1.018</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. KURUCS</t>
+          <t>T. LUWAWU-CABARROT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5608</v>
+        <v>1.2584</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7097</v>
+        <v>2.0901</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1488</v>
+        <v>-0.8318</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.3119</v>
+        <v>0.2337</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.8269</v>
+        <v>-0.253</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.485</v>
+        <v>0.4867</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9172</v>
+        <v>2.3354</v>
       </c>
       <c r="K15" t="n">
-        <v>1.0319</v>
+        <v>0.4374</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.1147</v>
+        <v>1.898</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.2292</v>
+        <v>-2.1017</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.8588</v>
+        <v>-0.6904</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.3703</v>
+        <v>-1.4113</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.2268</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1342</v>
+        <v>-3.4145</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9073</v>
+        <v>0.6829</v>
       </c>
       <c r="S15" t="n">
-        <v>3.2603</v>
+        <v>1.0325</v>
       </c>
       <c r="T15" t="n">
-        <v>1.9266</v>
+        <v>0.4455</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3337</v>
+        <v>0.587</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.1607</v>
+        <v>2.7237</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.7237</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. FRISCH</t>
+          <t>M. HOWARD</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1337</v>
+        <v>0.3077</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1567</v>
+        <v>0.8391999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2904</v>
+        <v>-0.5315</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3188</v>
+        <v>-2.2001</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.153</v>
+        <v>-0.6182</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4718</v>
+        <v>-1.5819</v>
       </c>
       <c r="J16" t="n">
-        <v>0.052</v>
+        <v>-0.5393</v>
       </c>
       <c r="K16" t="n">
-        <v>0.052</v>
+        <v>1.2788</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-1.818</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2669</v>
+        <v>-1.6608</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.205</v>
+        <v>-1.897</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4718</v>
+        <v>0.2361</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2268</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2268</v>
+        <v>0.9105</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4119</v>
+        <v>0.0604</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2087</v>
+        <v>-0.1584</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2032</v>
+        <v>0.2189</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>3.8132</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>3.8132</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T. LUWAWU-CABARROT</t>
+          <t>C. FRISCH</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0201</v>
+        <v>0.2012</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2074</v>
+        <v>-0.1574</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.1873</v>
+        <v>0.3586</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2388</v>
+        <v>0.3242</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2569</v>
+        <v>-0.1495</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4957</v>
+        <v>0.4738</v>
       </c>
       <c r="J17" t="n">
-        <v>2.3803</v>
+        <v>0.0517</v>
       </c>
       <c r="K17" t="n">
-        <v>0.4533</v>
+        <v>0.0517</v>
       </c>
       <c r="L17" t="n">
-        <v>1.9269</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.1415</v>
+        <v>0.2725</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7103</v>
+        <v>-0.2012</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.4312</v>
+        <v>0.4738</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.722</v>
+        <v>0.2276</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.4025</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6805</v>
+        <v>0.2276</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2284</v>
+        <v>-0.3507</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.502</v>
+        <v>-0.2091</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2737</v>
+        <v>-0.1416</v>
       </c>
       <c r="V17" t="n">
-        <v>2.7317</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.7317</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T. SEDEKERSKIS</t>
+          <t>R. KURUCS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1001</v>
+        <v>0.1793</v>
       </c>
       <c r="E18" t="n">
-        <v>0.364</v>
+        <v>0.7517</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4641</v>
+        <v>-0.5724</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1089</v>
+        <v>-1.289</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0403</v>
+        <v>-0.819</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1493</v>
+        <v>-0.4701</v>
       </c>
       <c r="J18" t="n">
-        <v>1.2467</v>
+        <v>0.9008</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3565</v>
+        <v>1.0202</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8902</v>
+        <v>-0.1194</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.3557</v>
+        <v>-2.1899</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3162</v>
+        <v>-1.8392</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.0395</v>
+        <v>-0.3507</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.6805</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4537</v>
+        <v>0.9105</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5286999999999999</v>
+        <v>1.8537</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0907</v>
+        <v>0.989</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4379</v>
+        <v>0.8647</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. HOWARD</t>
+          <t>T. SEDEKERSKIS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0561</v>
+        <v>-0.1917</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1776</v>
+        <v>0.3386</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2337</v>
+        <v>-0.5302</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.2141</v>
+        <v>-0.1033</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6308</v>
+        <v>0.0457</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.5833</v>
+        <v>-0.1489</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5104</v>
+        <v>1.2263</v>
       </c>
       <c r="K19" t="n">
-        <v>1.2917</v>
+        <v>0.348</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.802</v>
+        <v>0.8783</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.7037</v>
+        <v>-1.3296</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.9224</v>
+        <v>-0.3023</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2187</v>
+        <v>-1.0273</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.361</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9073</v>
+        <v>0.4553</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.3053</v>
+        <v>0.4367</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.868</v>
+        <v>0.0926</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4374</v>
+        <v>0.3441</v>
       </c>
       <c r="V19" t="n">
-        <v>3.8243</v>
+        <v>0.1578</v>
       </c>
       <c r="W19" t="n">
-        <v>3.8243</v>
+        <v>0.1578</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.079</v>
+        <v>-1.131</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9707</v>
+        <v>-1.1106</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1083</v>
+        <v>-0.0203</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.523</v>
+        <v>-1.5212</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.5843</v>
+        <v>-1.5853</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0613</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3991</v>
+        <v>-0.4204</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.4413</v>
+        <v>-1.4554</v>
       </c>
       <c r="L20" t="n">
-        <v>1.0422</v>
+        <v>1.035</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1239</v>
+        <v>-1.1007</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1431</v>
+        <v>-0.13</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.9808</v>
+        <v>-0.9708</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8977000000000001</v>
+        <v>0.8455</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5626</v>
+        <v>0.448</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3351</v>
+        <v>0.3975</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.1359</v>
+        <v>-1.817</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7381</v>
+        <v>-2.218</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6022</v>
+        <v>0.401</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.7282</v>
+        <v>-0.714</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.8428</v>
+        <v>-0.8334</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1147</v>
+        <v>0.1194</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1612</v>
+        <v>0.1607</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0866</v>
+        <v>0.0862</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8894</v>
+        <v>-0.8747</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.9294</v>
+        <v>-0.9196</v>
       </c>
       <c r="O21" t="n">
-        <v>0.04</v>
+        <v>0.0449</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S21" t="n">
-        <v>1.0213</v>
+        <v>0.3311</v>
       </c>
       <c r="T21" t="n">
-        <v>0.369</v>
+        <v>-0.1024</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6524</v>
+        <v>0.4335</v>
       </c>
       <c r="V21" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="22">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.0364</v>
+        <v>-1.8213</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.1318</v>
+        <v>-1.0177</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9046</v>
+        <v>-0.8036</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.5807</v>
+        <v>-0.5729</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.3435</v>
+        <v>-0.3391</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2372</v>
+        <v>-0.2337</v>
       </c>
       <c r="J22" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.0717</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.6526</v>
+        <v>-0.6446</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3781</v>
+        <v>-0.3736</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2745</v>
+        <v>-0.271</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3215</v>
+        <v>-0.1103</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0696</v>
+        <v>0.0487</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2519</v>
+        <v>-0.159</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>H. DIALLO</t>
+          <t>K. SIMMONS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.0458</v>
+        <v>-2.7989</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.0494</v>
+        <v>-1.7913</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9965000000000001</v>
+        <v>-1.0076</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.8138</v>
+        <v>-3.0162</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.8005</v>
+        <v>-1.7489</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.0133</v>
+        <v>-1.2674</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.3304</v>
+        <v>-0.9827</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.1784</v>
+        <v>-0.1109</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.152</v>
+        <v>-0.8718</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.4834</v>
+        <v>-2.0335</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.6221</v>
+        <v>-1.638</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1387</v>
+        <v>-0.3956</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.5878</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2631</v>
+        <v>0.9489</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4567</v>
+        <v>0.3782</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1936</v>
+        <v>0.5707</v>
       </c>
       <c r="V23" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W23" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>K. SIMMONS</t>
+          <t>H. DIALLO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.1493</v>
+        <v>-2.9894</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.1087</v>
+        <v>-2.3282</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.0405</v>
+        <v>-0.6612</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.0185</v>
+        <v>-2.8269</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.7445</v>
+        <v>-2.8166</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.2741</v>
+        <v>-0.0103</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.9543</v>
+        <v>-1.3642</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.0906</v>
+        <v>-1.2076</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.8637</v>
+        <v>-0.1566</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.0643</v>
+        <v>-1.4628</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.6539</v>
+        <v>-1.6091</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.4104</v>
+        <v>0.1463</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.8147</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R24" t="n">
-        <v>0.4537</v>
+        <v>0.6829</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5913</v>
+        <v>0.3414</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0212</v>
+        <v>0.2228</v>
       </c>
       <c r="U24" t="n">
-        <v>0.5701000000000001</v>
+        <v>0.1187</v>
       </c>
       <c r="V24" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W24" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.516299999999999</v>
+        <v>-6.725199999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.3081</v>
+        <v>-0.6019000000000003</v>
       </c>
       <c r="F25" t="n">
-        <v>-7.208100000000001</v>
+        <v>-6.1233</v>
       </c>
       <c r="G25" t="n">
-        <v>-10.3787</v>
+        <v>-10.3218</v>
       </c>
       <c r="H25" t="n">
-        <v>-8.4199</v>
+        <v>-8.4017</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.9589</v>
+        <v>-1.9198</v>
       </c>
       <c r="J25" t="n">
-        <v>4.641400000000001</v>
+        <v>4.421799999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>2.296400000000001</v>
+        <v>2.1614</v>
       </c>
       <c r="L25" t="n">
-        <v>2.3449</v>
+        <v>2.2605</v>
       </c>
       <c r="M25" t="n">
-        <v>-15.0202</v>
+        <v>-14.7437</v>
       </c>
       <c r="N25" t="n">
-        <v>-10.7164</v>
+        <v>-10.5633</v>
       </c>
       <c r="O25" t="n">
-        <v>-4.3038</v>
+        <v>-4.1805</v>
       </c>
       <c r="P25" t="n">
-        <v>-12.4759</v>
+        <v>-12.5199</v>
       </c>
       <c r="Q25" t="n">
-        <v>-18.1467</v>
+        <v>-18.2107</v>
       </c>
       <c r="R25" t="n">
-        <v>5.6708</v>
+        <v>5.6908</v>
       </c>
       <c r="S25" t="n">
-        <v>6.275700000000001</v>
+        <v>7.084700000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>3.2665</v>
+        <v>3.295</v>
       </c>
       <c r="U25" t="n">
-        <v>3.0092</v>
+        <v>3.7899</v>
       </c>
       <c r="V25" t="n">
-        <v>9.062799999999999</v>
+        <v>9.031500000000001</v>
       </c>
       <c r="W25" t="n">
-        <v>9.930600000000002</v>
+        <v>9.891699999999998</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.8678000000000001</v>
+        <v>-0.8602999999999998</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104521_W7.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104521_W7.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104521_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104521_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104521_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104521_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104521_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104521_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104521_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104521_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104521_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104521_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104521_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-9.891599999999999</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104521_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104521_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104521_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104521_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104521_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104521_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104521_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104521_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104521_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104521_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104521_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-0.8602999999999998</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
